--- a/data/trans_orig/P36BPD02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023</t>
+          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023 (tasa de respuesta: 96,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77368</t>
+          <t>79295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61245</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100508</t>
+          <t>103659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111322</t>
+          <t>109762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168613</t>
+          <t>167159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137008</t>
+          <t>135876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200657</t>
+          <t>199777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114886</t>
+          <t>112163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160338</t>
+          <t>157547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266686</t>
+          <t>267999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344577</t>
+          <t>341341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92660</t>
+          <t>89626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155163</t>
+          <t>156531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58836</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99843</t>
+          <t>97710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163282</t>
+          <t>161937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240422</t>
+          <t>236887</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55796</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98374</t>
+          <t>95033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46302</t>
+          <t>45940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100878</t>
+          <t>102053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118484</t>
+          <t>114891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187647</t>
+          <t>183120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149548</t>
+          <t>148748</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>199289</t>
+          <t>202215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118028</t>
+          <t>109972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225001</t>
+          <t>220943</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>273949</t>
+          <t>273718</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>403789</t>
+          <t>402547</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135288</t>
+          <t>136092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189941</t>
+          <t>187839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175050</t>
+          <t>175811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>323942</t>
+          <t>335318</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>333895</t>
+          <t>335902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>508070</t>
+          <t>523008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>69331</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>104787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60792</t>
+          <t>60672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87999</t>
+          <t>86812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138184</t>
+          <t>136556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182393</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216121</t>
+          <t>219992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>263250</t>
+          <t>264821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215390</t>
+          <t>218412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254840</t>
+          <t>254910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445632</t>
+          <t>445004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>506421</t>
+          <t>505801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164995</t>
+          <t>167453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212743</t>
+          <t>211356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197314</t>
+          <t>198063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235211</t>
+          <t>233939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378305</t>
+          <t>376752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435523</t>
+          <t>436598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37477</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131543</t>
+          <t>131873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63722</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94363</t>
+          <t>95472</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106573</t>
+          <t>99607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212649</t>
+          <t>209538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134583</t>
+          <t>123644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418711</t>
+          <t>418033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306485</t>
+          <t>306819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391437</t>
+          <t>400172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398502</t>
+          <t>396681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>759244</t>
+          <t>754799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>325292</t>
+          <t>325459</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>695771</t>
+          <t>707393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237705</t>
+          <t>234273</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>306069</t>
+          <t>305314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>604475</t>
+          <t>606741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1047171</t>
+          <t>1059225</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>55494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>84253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>60336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84365</t>
+          <t>83796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121346</t>
+          <t>122422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160564</t>
+          <t>158631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>216890</t>
+          <t>216150</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>260767</t>
+          <t>260621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>233085</t>
+          <t>232928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>266736</t>
+          <t>267677</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>464342</t>
+          <t>465039</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>517738</t>
+          <t>516800</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205000</t>
+          <t>203346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>248242</t>
+          <t>249254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190624</t>
+          <t>189503</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223188</t>
+          <t>223527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>407395</t>
+          <t>404581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>460379</t>
+          <t>457459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47519</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73972</t>
+          <t>75768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41243</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>113537</t>
+          <t>111597</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>158355</t>
+          <t>158173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188589</t>
+          <t>186879</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69607</t>
+          <t>59145</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>285709</t>
+          <t>284099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171219</t>
+          <t>189681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>462099</t>
+          <t>460914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124974</t>
+          <t>124790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154397</t>
+          <t>154825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>241725</t>
+          <t>241831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>510365</t>
+          <t>520911</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>377780</t>
+          <t>378901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>737300</t>
+          <t>713339</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51382</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>70938</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82079</t>
+          <t>81032</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>108925</t>
+          <t>107490</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117462</t>
+          <t>118518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143807</t>
+          <t>144267</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>195582</t>
+          <t>193786</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>222765</t>
+          <t>221903</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>320650</t>
+          <t>321093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>357160</t>
+          <t>358585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87793</t>
+          <t>86655</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112308</t>
+          <t>112365</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>112448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138246</t>
+          <t>138388</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>206636</t>
+          <t>208757</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>243795</t>
+          <t>244438</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>331562</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>500955</t>
+          <t>496845</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>402364</t>
+          <t>396161</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>544077</t>
+          <t>549400</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>812749</t>
+          <t>796082</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1010541</t>
+          <t>1017847</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1092043</t>
+          <t>1059384</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1552674</t>
+          <t>1546941</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1255156</t>
+          <t>1207835</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1662853</t>
+          <t>1667796</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2547836</t>
+          <t>2531860</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3162104</t>
+          <t>3151034</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1253722</t>
+          <t>1260347</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1846244</t>
+          <t>1879156</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1336762</t>
+          <t>1329386</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1880700</t>
+          <t>1927753</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2661458</t>
+          <t>2666294</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3471391</t>
+          <t>3458948</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54796</t>
+          <t>68206</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79295</t>
+          <t>92070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>80797</t>
+          <t>93591</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>72434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103659</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>161797</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109762</t>
+          <t>131362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167159</t>
+          <t>193548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>167246</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135876</t>
+          <t>143215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199777</t>
+          <t>201149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>136574</t>
+          <t>158854</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>132010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157547</t>
+          <t>181898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>303819</t>
+          <t>330241</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267999</t>
+          <t>294264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341341</t>
+          <t>369197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122445</t>
+          <t>114427</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89626</t>
+          <t>87842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156531</t>
+          <t>145622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77557</t>
+          <t>90528</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58710</t>
+          <t>69841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97710</t>
+          <t>114537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>200001</t>
+          <t>204955</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>161937</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236887</t>
+          <t>238470</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>354020</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>354020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>354020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>294928</t>
+          <t>342973</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>294928</t>
+          <t>342973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294928</t>
+          <t>342973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>639414</t>
+          <t>696993</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>639414</t>
+          <t>696993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>639414</t>
+          <t>696993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74902</t>
+          <t>95688</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>73989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95033</t>
+          <t>118856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79316</t>
+          <t>99565</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45940</t>
+          <t>82252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102053</t>
+          <t>118417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>154218</t>
+          <t>195253</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114891</t>
+          <t>170420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183120</t>
+          <t>227296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175234</t>
+          <t>192316</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148748</t>
+          <t>166336</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202215</t>
+          <t>221320</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>202397</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109972</t>
+          <t>180117</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220943</t>
+          <t>223446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>357504</t>
+          <t>394713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>273718</t>
+          <t>357664</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>402547</t>
+          <t>427805</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>161032</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136092</t>
+          <t>143986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187839</t>
+          <t>197008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>228847</t>
+          <t>172414</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175811</t>
+          <t>150544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>335318</t>
+          <t>196702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>389879</t>
+          <t>343194</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>335902</t>
+          <t>310012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>523008</t>
+          <t>379937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>411167</t>
+          <t>458784</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>411167</t>
+          <t>458784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>411167</t>
+          <t>458784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>490434</t>
+          <t>474376</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>490434</t>
+          <t>474376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490434</t>
+          <t>474376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>901601</t>
+          <t>933160</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>901601</t>
+          <t>933160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>901601</t>
+          <t>933160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85469</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69331</t>
+          <t>96238</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104787</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73208</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>73595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86812</t>
+          <t>101201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>158677</t>
+          <t>202201</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136556</t>
+          <t>178453</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>183952</t>
+          <t>228218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>240519</t>
+          <t>265774</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219992</t>
+          <t>239420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>264821</t>
+          <t>293462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>236309</t>
+          <t>273261</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>252940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254910</t>
+          <t>294713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>476828</t>
+          <t>539034</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445004</t>
+          <t>506801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505801</t>
+          <t>569005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>191491</t>
+          <t>215404</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167453</t>
+          <t>189983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211356</t>
+          <t>244083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>215607</t>
+          <t>242637</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198063</t>
+          <t>224572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>233939</t>
+          <t>263527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>407097</t>
+          <t>458041</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376752</t>
+          <t>428683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>436598</t>
+          <t>489303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517479</t>
+          <t>596020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517479</t>
+          <t>596020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>517479</t>
+          <t>596020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>525124</t>
+          <t>603256</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>525124</t>
+          <t>603256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>525124</t>
+          <t>603256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1042603</t>
+          <t>1199276</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1042603</t>
+          <t>1199276</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1042603</t>
+          <t>1199276</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>89950</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31883</t>
+          <t>73056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131873</t>
+          <t>109978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80051</t>
+          <t>94784</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64593</t>
+          <t>80847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95472</t>
+          <t>109437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>184734</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99607</t>
+          <t>160812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209538</t>
+          <t>208719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>289520</t>
+          <t>319169</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123644</t>
+          <t>295430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418033</t>
+          <t>346693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>333101</t>
+          <t>329159</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306819</t>
+          <t>308848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400172</t>
+          <t>349892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>622621</t>
+          <t>648328</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396681</t>
+          <t>617124</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>754799</t>
+          <t>683010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>488512</t>
+          <t>264802</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>325459</t>
+          <t>239719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>707393</t>
+          <t>290376</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>281608</t>
+          <t>294529</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>234273</t>
+          <t>274276</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>314341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>770121</t>
+          <t>559330</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>606741</t>
+          <t>526378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1059225</t>
+          <t>592363</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>864474</t>
+          <t>673920</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>864474</t>
+          <t>673920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>864474</t>
+          <t>673920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>694760</t>
+          <t>718472</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>694760</t>
+          <t>718472</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>694760</t>
+          <t>718472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1559235</t>
+          <t>1392392</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1559235</t>
+          <t>1392392</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1559235</t>
+          <t>1392392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55494</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84253</t>
+          <t>94484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>71814</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60336</t>
+          <t>70069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83796</t>
+          <t>96235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>140398</t>
+          <t>161455</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122422</t>
+          <t>141734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>158631</t>
+          <t>182842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>238676</t>
+          <t>261473</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>216150</t>
+          <t>240456</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>260621</t>
+          <t>283719</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>251453</t>
+          <t>282822</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>232928</t>
+          <t>263378</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>267677</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>490129</t>
+          <t>544295</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>465039</t>
+          <t>515237</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>516800</t>
+          <t>574831</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>226201</t>
+          <t>238376</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203346</t>
+          <t>215516</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249254</t>
+          <t>259866</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>206668</t>
+          <t>224212</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189503</t>
+          <t>207421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223527</t>
+          <t>243553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>432869</t>
+          <t>462588</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>404581</t>
+          <t>431894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457459</t>
+          <t>491362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>533461</t>
+          <t>579173</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>533461</t>
+          <t>579173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>533461</t>
+          <t>579173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>529935</t>
+          <t>589165</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>529935</t>
+          <t>589165</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>529935</t>
+          <t>589165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1063396</t>
+          <t>1168338</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1063396</t>
+          <t>1168338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1063396</t>
+          <t>1168338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37860</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29876</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>51309</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>42793</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>62546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>93776</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>80292</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>111597</t>
+          <t>109937</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>172364</t>
+          <t>191641</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>158173</t>
+          <t>175301</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>186879</t>
+          <t>207570</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>183316</t>
+          <t>202300</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59145</t>
+          <t>187292</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>284099</t>
+          <t>216498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>355680</t>
+          <t>393941</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189681</t>
+          <t>372325</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>460914</t>
+          <t>416471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>139684</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124790</t>
+          <t>136589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154825</t>
+          <t>168529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>367388</t>
+          <t>172433</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>241831</t>
+          <t>157713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>520911</t>
+          <t>186807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>507072</t>
+          <t>325462</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>378901</t>
+          <t>303660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>713339</t>
+          <t>346148</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>349907</t>
+          <t>387137</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>349907</t>
+          <t>387137</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>349907</t>
+          <t>387137</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>596949</t>
+          <t>426042</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>596949</t>
+          <t>426042</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>596949</t>
+          <t>426042</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>946856</t>
+          <t>813179</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>946856</t>
+          <t>813179</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>946856</t>
+          <t>813179</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>47545</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61062</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>56093</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>70938</t>
+          <t>77110</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>94208</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81032</t>
+          <t>90261</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107490</t>
+          <t>119504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>130866</t>
+          <t>145052</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118518</t>
+          <t>129898</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144267</t>
+          <t>159591</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>208213</t>
+          <t>229687</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193786</t>
+          <t>212970</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>221903</t>
+          <t>244063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>339079</t>
+          <t>374739</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>321093</t>
+          <t>354644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>358585</t>
+          <t>395882</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>99622</t>
+          <t>106190</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86655</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112365</t>
+          <t>118890</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>135961</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112448</t>
+          <t>121558</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138388</t>
+          <t>152119</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>225053</t>
+          <t>242151</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>208757</t>
+          <t>221663</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>244438</t>
+          <t>261988</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>263634</t>
+          <t>288712</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>263634</t>
+          <t>288712</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>263634</t>
+          <t>288712</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>394706</t>
+          <t>431605</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>394706</t>
+          <t>431605</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>394706</t>
+          <t>431605</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>658340</t>
+          <t>720317</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>658340</t>
+          <t>720317</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>658340</t>
+          <t>720317</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>441198</t>
+          <t>527947</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>331562</t>
+          <t>480993</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>496845</t>
+          <t>572113</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>492494</t>
+          <t>574695</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>396161</t>
+          <t>534038</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>549400</t>
+          <t>612870</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>933691</t>
+          <t>1102642</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>796082</t>
+          <t>1044692</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1017847</t>
+          <t>1158614</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1414425</t>
+          <t>1546811</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1059384</t>
+          <t>1483131</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1546941</t>
+          <t>1612345</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1531237</t>
+          <t>1678480</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1207835</t>
+          <t>1625840</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1667796</t>
+          <t>1734171</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2945662</t>
+          <t>3225291</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2531860</t>
+          <t>3142902</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3151034</t>
+          <t>3306702</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1428987</t>
+          <t>1263009</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1260347</t>
+          <t>1195506</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1879156</t>
+          <t>1324237</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1503105</t>
+          <t>1332713</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1329386</t>
+          <t>1273930</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1927753</t>
+          <t>1380520</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2932092</t>
+          <t>2595722</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2666294</t>
+          <t>2515535</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3458948</t>
+          <t>2678539</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
